--- a/data/trans_orig/Q5417-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2007</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -846,97 +846,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105878</t>
+          <t>106375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114048</t>
+          <t>114104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137026</t>
+          <t>137129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147274</t>
+          <t>148335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>248094</t>
+          <t>246651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260433</t>
+          <t>259916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>135042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144846</t>
+          <t>144855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164522</t>
+          <t>163890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178064</t>
+          <t>177473</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>306262</t>
+          <t>305460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321052</t>
+          <t>320798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -1871,97 +1871,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1984,97 +1984,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>897</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99510</t>
+          <t>99192</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119636</t>
+          <t>120373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131653</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223370</t>
+          <t>222864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235696</t>
+          <t>235794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128902</t>
+          <t>129634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136393</t>
+          <t>136382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191487</t>
+          <t>191994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203959</t>
+          <t>204377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324094</t>
+          <t>325220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>338899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23106</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>481003</t>
+          <t>483452</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>495606</t>
+          <t>495829</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>630461</t>
+          <t>629853</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>653490</t>
+          <t>653390</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1118939</t>
+          <t>1118150</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1145238</t>
+          <t>1144688</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2012</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128773</t>
+          <t>128313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137575</t>
+          <t>137555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146732</t>
+          <t>146528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160365</t>
+          <t>160434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279552</t>
+          <t>280394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295785</t>
+          <t>296607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13632</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135975</t>
+          <t>134610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149415</t>
+          <t>149286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>156304</t>
+          <t>157303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175672</t>
+          <t>176243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>297549</t>
+          <t>299023</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321491</t>
+          <t>321681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89690</t>
+          <t>89742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101532</t>
+          <t>101643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122280</t>
+          <t>120649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135838</t>
+          <t>135863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216821</t>
+          <t>216650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235781</t>
+          <t>235608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150623</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159686</t>
+          <t>159708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>215372</t>
+          <t>214593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>232058</t>
+          <t>232265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>371388</t>
+          <t>371273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390412</t>
+          <t>389968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23900</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>31978</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49499</t>
+          <t>50610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>38076</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69323</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>521570</t>
+          <t>522689</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>542817</t>
+          <t>542791</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>658946</t>
+          <t>659558</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>690906</t>
+          <t>692067</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1189931</t>
+          <t>1189090</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1227967</t>
+          <t>1227308</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2016</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124219</t>
+          <t>124121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133442</t>
+          <t>133461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154406</t>
+          <t>155209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167935</t>
+          <t>168424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>282816</t>
+          <t>283705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300069</t>
+          <t>299985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153496</t>
+          <t>153521</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162380</t>
+          <t>162375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>198467</t>
+          <t>200263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>214616</t>
+          <t>214601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>357938</t>
+          <t>355851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375370</t>
+          <t>374652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -8025,97 +8025,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8459</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2618</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8937</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7944</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>9309</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,62 +8173,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2297</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4019</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4082</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>109844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116662</t>
+          <t>116719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133077</t>
+          <t>133919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229351</t>
+          <t>228007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247194</t>
+          <t>247392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -8594,97 +8594,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173019</t>
+          <t>173048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223741</t>
+          <t>224398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238828</t>
+          <t>238744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>391994</t>
+          <t>390571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408768</t>
+          <t>408608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23371</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>20266</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21492</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46891</t>
+          <t>45813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30347</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57589</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>562398</t>
+          <t>562283</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>578675</t>
+          <t>578740</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714734</t>
+          <t>714900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>744514</t>
+          <t>745027</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1284549</t>
+          <t>1285246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1318318</t>
+          <t>1318478</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2023</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139177</t>
+          <t>139006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145434</t>
+          <t>145527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159634</t>
+          <t>159699</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168687</t>
+          <t>168381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301418</t>
+          <t>301365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312292</t>
+          <t>312413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148075</t>
+          <t>147644</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156639</t>
+          <t>156026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194321</t>
+          <t>195079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206327</t>
+          <t>206874</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>346071</t>
+          <t>346845</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>360718</t>
+          <t>360687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -11102,97 +11102,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9259</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2972</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9569</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8516</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>8577</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -11215,97 +11215,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3944</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4701</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4009</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128389</t>
+          <t>128187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135502</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>331560</t>
+          <t>332393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357982</t>
+          <t>358233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470305</t>
+          <t>468509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>493051</t>
+          <t>493104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199206</t>
+          <t>198749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204377</t>
+          <t>204364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>254584</t>
+          <t>255089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265875</t>
+          <t>265964</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457082</t>
+          <t>457579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>468986</t>
+          <t>469102</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50989</t>
+          <t>51716</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>64629</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>624422</t>
+          <t>624285</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>637774</t>
+          <t>637493</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>958703</t>
+          <t>958218</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1006263</t>
+          <t>1004838</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1591263</t>
+          <t>1593038</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1633077</t>
+          <t>1635876</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5417-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>106604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114104</t>
+          <t>114043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137129</t>
+          <t>136617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148335</t>
+          <t>147257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>246651</t>
+          <t>246931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259916</t>
+          <t>260058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20503</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135042</t>
+          <t>136676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>144853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>163700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177473</t>
+          <t>177518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>305460</t>
+          <t>305254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>320798</t>
+          <t>321039</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99192</t>
+          <t>99480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120373</t>
+          <t>119886</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131790</t>
+          <t>131749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222864</t>
+          <t>222193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235794</t>
+          <t>235638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129634</t>
+          <t>129522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136382</t>
+          <t>136387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191994</t>
+          <t>191587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204377</t>
+          <t>204590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325220</t>
+          <t>325823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>338899</t>
+          <t>338944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>483452</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>495536</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>629853</t>
+          <t>630344</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>653390</t>
+          <t>652980</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1118150</t>
+          <t>1118670</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1144688</t>
+          <t>1145320</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128313</t>
+          <t>128985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137555</t>
+          <t>137607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146528</t>
+          <t>146704</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160434</t>
+          <t>160435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280394</t>
+          <t>278446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>296607</t>
+          <t>296219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24719</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32380</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134610</t>
+          <t>136142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149286</t>
+          <t>149466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157303</t>
+          <t>156396</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176243</t>
+          <t>175720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>299023</t>
+          <t>297696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321681</t>
+          <t>320473</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89742</t>
+          <t>89448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101643</t>
+          <t>101620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120649</t>
+          <t>121774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135863</t>
+          <t>135706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216650</t>
+          <t>219361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235608</t>
+          <t>235444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>151157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159708</t>
+          <t>159700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214593</t>
+          <t>215052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>232265</t>
+          <t>232242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>371273</t>
+          <t>369767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>389968</t>
+          <t>389701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>66716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>522689</t>
+          <t>520565</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>542791</t>
+          <t>541850</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>659558</t>
+          <t>661364</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>692067</t>
+          <t>692557</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1189090</t>
+          <t>1192444</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1227308</t>
+          <t>1228512</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124121</t>
+          <t>124172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133461</t>
+          <t>133509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155209</t>
+          <t>155097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168424</t>
+          <t>168265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>283705</t>
+          <t>283701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299985</t>
+          <t>300008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153521</t>
+          <t>153263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162375</t>
+          <t>162371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200263</t>
+          <t>200536</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>214601</t>
+          <t>215186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>355851</t>
+          <t>359097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374652</t>
+          <t>375321</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109844</t>
+          <t>108960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116719</t>
+          <t>117246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133919</t>
+          <t>133637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228007</t>
+          <t>229034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247392</t>
+          <t>246395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162111</t>
+          <t>162356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173048</t>
+          <t>172582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224398</t>
+          <t>222952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238744</t>
+          <t>237671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390571</t>
+          <t>391711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408608</t>
+          <t>408419</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,34 +9183,34 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>18432</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>19016</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45813</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>58794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>562283</t>
+          <t>561678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>578740</t>
+          <t>578810</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714900</t>
+          <t>713987</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>744826</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1285246</t>
+          <t>1285667</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1318478</t>
+          <t>1318480</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>143011</t>
+          <t>158072</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139006</t>
+          <t>153562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145527</t>
+          <t>160548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>164561</t>
+          <t>175889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159699</t>
+          <t>170971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168381</t>
+          <t>180241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>307572</t>
+          <t>333961</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301365</t>
+          <t>327170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312413</t>
+          <t>339121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>147560</t>
+          <t>162813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147560</t>
+          <t>162813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147560</t>
+          <t>162813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>178816</t>
+          <t>190684</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>178816</t>
+          <t>190684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178816</t>
+          <t>190684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>326376</t>
+          <t>353497</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>326376</t>
+          <t>353497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326376</t>
+          <t>353497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,22 +10563,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>10588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>22620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>152871</t>
+          <t>170582</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147644</t>
+          <t>165062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156026</t>
+          <t>174144</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>201376</t>
+          <t>223853</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>195079</t>
+          <t>216457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206874</t>
+          <t>228790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>354247</t>
+          <t>394434</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>346845</t>
+          <t>385781</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>360687</t>
+          <t>401641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>133091</t>
+          <t>155433</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128187</t>
+          <t>150660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135656</t>
+          <t>158143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>349533</t>
+          <t>163521</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>332393</t>
+          <t>156329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>358233</t>
+          <t>168002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>482626</t>
+          <t>318954</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>468509</t>
+          <t>312051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>493104</t>
+          <t>324534</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,17 +11736,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -11902,12 +11902,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202862</t>
+          <t>212517</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198749</t>
+          <t>208712</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204364</t>
+          <t>214433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>261268</t>
+          <t>278145</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255089</t>
+          <t>270240</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265964</t>
+          <t>283882</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>464131</t>
+          <t>490660</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457579</t>
+          <t>481126</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>469102</t>
+          <t>496769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -12245,22 +12245,22 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>41408</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64629</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -12574,22 +12574,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>631836</t>
+          <t>696602</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>624285</t>
+          <t>687906</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>637493</t>
+          <t>702606</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>976739</t>
+          <t>841408</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>958218</t>
+          <t>831017</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1004838</t>
+          <t>852541</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1608575</t>
+          <t>1538009</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1593038</t>
+          <t>1522743</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1635876</t>
+          <t>1549634</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
